--- a/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="5130" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O42" headerRowCount="1">
-  <autoFilter ref="A1:O42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O72" headerRowCount="1">
+  <autoFilter ref="A1:O72"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -536,7 +536,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="30" customWidth="1" style="12" min="1" max="1"/>
     <col width="95" customWidth="1" style="12" min="2" max="2"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.6" customHeight="1" s="12">
+    <row r="3" ht="15.65" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Overview</t>
@@ -570,7 +570,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.6" customHeight="1" s="12">
+    <row r="8" ht="15.65" customHeight="1" s="12">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>What to do</t>
@@ -667,7 +667,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.6" customHeight="1" s="12">
+    <row r="19" ht="15.65" customHeight="1" s="12">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
@@ -725,7 +725,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
     <col width="16" customWidth="1" style="12" min="3" max="3"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O2" s="10" t="n"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="10" t="n"/>
@@ -2925,8 +2925,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:O72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
     <col width="16" customWidth="1" style="12" min="3" max="3"/>
@@ -4658,21 +4658,1217 @@
       </c>
       <c r="M42" s="10" t="n"/>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp4</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp9</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kekeno</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp11</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp12</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp13</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp26</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp27</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp28</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp29</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp14</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>non_idp_NG002010_supp16</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>idp_NG002010_supp1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>idp_NG002010_supp2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>idp_NG002010_supp3</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp10</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp11</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp2</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp3</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp4</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp5</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp6</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp7</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp8</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>idp_NG008024_supp9</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
+    <dataValidation sqref="M2:M72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-7-1</formula1>
     </dataValidation>
   </dataValidations>
@@ -4939,13 +6135,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D5EAC89-10A5-4BC6-B891-0F334D1072CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85457CDF-7FE2-4DB2-B1DD-4955F2E6D33F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ABE7739-3F10-40EE-B719-201CB7C08569}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{844159E7-6BBC-4D7C-8476-272B3102B8C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DCC1BCD-0011-48E7-8AA0-ECA6D3E96725}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{469983DF-5C2D-433C-888C-596A3C86A4EE}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O72" headerRowCount="1">
-  <autoFilter ref="A1:O72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O74" headerRowCount="1">
+  <autoFilter ref="A1:O74"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -2925,7 +2925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -4684,7 +4684,6 @@
           <t>non_idp_NG008024_supp3</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>6</t>
@@ -4722,7 +4721,6 @@
           <t>non_idp_NG002010_supp1</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>6</t>
@@ -4760,7 +4758,6 @@
           <t>non_idp_NG002010_supp2</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>6</t>
@@ -4798,7 +4795,6 @@
           <t>non_idp_NG002010_supp4</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>6</t>
@@ -4836,7 +4832,6 @@
           <t>non_idp_NG002010_supp9</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>6</t>
@@ -4874,7 +4869,6 @@
           <t>non_idp_NG008024_supp19</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>6</t>
@@ -4912,7 +4906,6 @@
           <t>non_idp_NG002010_supp11</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>6</t>
@@ -4950,7 +4943,6 @@
           <t>non_idp_NG002010_supp12</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>6</t>
@@ -4988,7 +4980,6 @@
           <t>non_idp_NG002010_supp13</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>6</t>
@@ -5026,7 +5017,6 @@
           <t>non_idp_NG008024_supp26</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>6</t>
@@ -5064,7 +5054,6 @@
           <t>non_idp_NG008024_supp27</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>6</t>
@@ -5102,7 +5091,6 @@
           <t>non_idp_NG008024_supp28</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>6</t>
@@ -5140,7 +5128,6 @@
           <t>non_idp_NG008024_supp29</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>6</t>
@@ -5178,7 +5165,6 @@
           <t>non_idp_NG008024_supp30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>6</t>
@@ -5216,7 +5202,6 @@
           <t>non_idp_NG002010_supp14</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>6</t>
@@ -5254,7 +5239,6 @@
           <t>non_idp_NG002010_supp16</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>6</t>
@@ -5854,21 +5838,97 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp31</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp32</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
+    <dataValidation sqref="M2:M74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-7-1</formula1>
     </dataValidation>
   </dataValidations>
@@ -5877,271 +5937,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85457CDF-7FE2-4DB2-B1DD-4955F2E6D33F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{844159E7-6BBC-4D7C-8476-272B3102B8C3}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{469983DF-5C2D-433C-888C-596A3C86A4EE}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O74" headerRowCount="1">
-  <autoFilter ref="A1:O74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O76" headerRowCount="1">
+  <autoFilter ref="A1:O76"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -2925,7 +2925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -5864,7 +5864,6 @@
           <t>non_idp_NG008024_supp31</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>6</t>
@@ -5902,13 +5901,88 @@
           <t>non_idp_NG008024_supp32</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp33</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>non_idp_NG008024_supp34</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -5916,19 +5990,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
+    <dataValidation sqref="M2:M76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-7-1</formula1>
     </dataValidation>
   </dataValidations>

--- a/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Street Child of Nigeria_accessibility_report.xlsx
@@ -6011,4 +6011,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77D6A97E-25C1-476A-BCD3-71B4D5E54F47}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE1F75E-2334-4233-B47A-9FEFF6DF0AC1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD4712C-B0BD-4A8C-A78E-1415E8044039}"/>
 </file>